--- a/e2e/downloadedFile/Non_Regular_Salary_Hometrip_Q1.xlsx
+++ b/e2e/downloadedFile/Non_Regular_Salary_Hometrip_Q1.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="46">
   <si>
     <t>DAFTAR PEMBAYARAN</t>
   </si>
@@ -59,109 +59,94 @@
     <t>MAR</t>
   </si>
   <si>
+    <t>CELIA MARIA REGO DE FATIMA</t>
+  </si>
+  <si>
+    <t>IV</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>550,00</t>
+  </si>
+  <si>
+    <t>0,00</t>
+  </si>
+  <si>
+    <t>1.100,00</t>
+  </si>
+  <si>
+    <t>60,00</t>
+  </si>
+  <si>
+    <t>ADROALDINO DA SILVA NORONHA TOME</t>
+  </si>
+  <si>
+    <t>VI</t>
+  </si>
+  <si>
+    <t>5,00</t>
+  </si>
+  <si>
+    <t>HERU YULIANTO</t>
+  </si>
+  <si>
+    <t>II</t>
+  </si>
+  <si>
+    <t>AHMAD RIYANA SAPUTRA</t>
+  </si>
+  <si>
+    <t>RIMBUN SIBURIAN</t>
+  </si>
+  <si>
+    <t>100,00</t>
+  </si>
+  <si>
+    <t>200,00</t>
+  </si>
+  <si>
+    <t>AGOSTINHO GOMES FERNANDES</t>
+  </si>
+  <si>
+    <t>Expat</t>
+  </si>
+  <si>
+    <t>SYALDY KHARISMA ANANDA</t>
+  </si>
+  <si>
+    <t>III</t>
+  </si>
+  <si>
+    <t>GRAND TOTAL</t>
+  </si>
+  <si>
+    <t>3.800,00</t>
+  </si>
+  <si>
+    <t>130,00</t>
+  </si>
+  <si>
+    <t>DILI, 18 August 2026</t>
+  </si>
+  <si>
+    <t>PREPARED BY</t>
+  </si>
+  <si>
+    <t>APPROVED BY</t>
+  </si>
+  <si>
+    <t>Human Resource</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Retail Senior Manager</t>
+  </si>
+  <si>
+    <t>Superadmin</t>
+  </si>
+  <si>
     <t>Lestari Putri Cantika</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>Homestaff</t>
-  </si>
-  <si>
-    <t>100,00</t>
-  </si>
-  <si>
-    <t>300,00</t>
-  </si>
-  <si>
-    <t>0,00</t>
-  </si>
-  <si>
-    <t>HELENA</t>
-  </si>
-  <si>
-    <t>II</t>
-  </si>
-  <si>
-    <t>FRIESCA AMELIA</t>
-  </si>
-  <si>
-    <t>III</t>
-  </si>
-  <si>
-    <t>Expat</t>
-  </si>
-  <si>
-    <t>10,00</t>
-  </si>
-  <si>
-    <t>30,00</t>
-  </si>
-  <si>
-    <t>Citra</t>
-  </si>
-  <si>
-    <t>dominika</t>
-  </si>
-  <si>
-    <t>IV</t>
-  </si>
-  <si>
-    <t>90,00</t>
-  </si>
-  <si>
-    <t>AGOSTINHO GOMES FERNANDES</t>
-  </si>
-  <si>
-    <t>VI</t>
-  </si>
-  <si>
-    <t>50,00</t>
-  </si>
-  <si>
-    <t>150,00</t>
-  </si>
-  <si>
-    <t>CELIA MARIA REGO DE FATIMA</t>
-  </si>
-  <si>
-    <t>Local</t>
-  </si>
-  <si>
-    <t>0000002</t>
-  </si>
-  <si>
-    <t>Syifa Hadju</t>
-  </si>
-  <si>
-    <t>25,00</t>
-  </si>
-  <si>
-    <t>75,00</t>
-  </si>
-  <si>
-    <t>GRAND TOTAL</t>
-  </si>
-  <si>
-    <t>1.395,00</t>
-  </si>
-  <si>
-    <t>DILI, 14 August 2026</t>
-  </si>
-  <si>
-    <t>PREPARED BY</t>
-  </si>
-  <si>
-    <t>APPROVED BY</t>
-  </si>
-  <si>
-    <t>Human Resource</t>
-  </si>
-  <si>
-    <t>Marketing &amp; Retail Senior Manager</t>
-  </si>
-  <si>
-    <t>Superadmin</t>
   </si>
   <si>
     <t>NIK. 000002</t>
@@ -260,7 +245,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="514350" cy="333375"/>
@@ -579,19 +564,19 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="true" style="0"/>
-    <col min="2" max="2" width="31.707" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="38.848" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="5.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="11.711" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="5.856" bestFit="true" customWidth="true" style="0"/>
     <col min="6" max="6" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="7" max="7" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="5.856" bestFit="true" customWidth="true" style="0"/>
     <col min="9" max="9" width="10.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="5.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="10" max="10" width="8.141" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -660,7 +645,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="3">
-        <v>999999</v>
+        <v>92003</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>14</v>
@@ -679,24 +664,24 @@
         <v>17</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="3">
-        <v>84016</v>
+        <v>24016</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>16</v>
@@ -706,60 +691,60 @@
         <v>17</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="3">
-        <v>91009</v>
+        <v>74003</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="3">
-        <v>900145</v>
+        <v>95008</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
@@ -769,43 +754,43 @@
         <v>17</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="3">
-        <v>83005</v>
+        <v>81010</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -813,164 +798,134 @@
         <v>26013</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="3">
-        <v>92003</v>
+        <v>91015</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="3" t="s">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="F16"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" t="s">
         <v>40</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="4" t="s">
+      <c r="E18"/>
+      <c r="G18" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="4" t="s">
+    </row>
+    <row r="19" spans="1:10" customHeight="1" ht="37.5">
+      <c r="A19"/>
+      <c r="E19"/>
+      <c r="G19"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J15" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16"/>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" t="s">
+      <c r="E20"/>
+      <c r="G20" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F17"/>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="5" t="s">
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5" t="s">
+      <c r="E21"/>
+      <c r="G21" t="s">
         <v>45</v>
-      </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" t="s">
-        <v>46</v>
-      </c>
-      <c r="E19"/>
-      <c r="G19" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" customHeight="1" ht="37.5">
-      <c r="A20"/>
-      <c r="E20"/>
-      <c r="G20"/>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E21"/>
-      <c r="G21" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" t="s">
-        <v>49</v>
-      </c>
-      <c r="E22"/>
-      <c r="G22" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -987,12 +942,15 @@
     <mergeCell ref="F5:H5"/>
     <mergeCell ref="I5:I6"/>
     <mergeCell ref="J5:J6"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="F16:J16"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="F17:J17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="F18:J18"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:J18"/>
     <mergeCell ref="A19:D19"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="G19:J19"/>
@@ -1002,9 +960,6 @@
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="E21:F21"/>
     <mergeCell ref="G21:J21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:J22"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
